--- a/src/notebooks/результаты_кластеризации.xlsx
+++ b/src/notebooks/результаты_кластеризации.xlsx
@@ -429,7 +429,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +443,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -513,7 +513,7 @@
         <v>4</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -695,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -835,7 +835,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -933,7 +933,7 @@
         <v>3</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -961,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>6</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1017,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -1143,7 +1143,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -1157,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -1339,7 +1339,7 @@
         <v>14</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -1353,7 +1353,7 @@
         <v>50</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -1507,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -1535,7 +1535,7 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -1633,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -1647,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="D92">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -1759,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -1773,7 +1773,7 @@
         <v>2</v>
       </c>
       <c r="D101">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -1815,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -1857,7 +1857,7 @@
         <v>2</v>
       </c>
       <c r="D107">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -1927,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -1941,7 +1941,7 @@
         <v>4</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -1983,7 +1983,7 @@
         <v>6</v>
       </c>
       <c r="D116">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -1997,7 +1997,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -2081,7 +2081,7 @@
         <v>4</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="D127">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -2179,7 +2179,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -2193,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -2221,7 +2221,7 @@
         <v>4</v>
       </c>
       <c r="D133">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -2277,7 +2277,7 @@
         <v>2</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -2305,7 +2305,7 @@
         <v>2</v>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2333,7 +2333,7 @@
         <v>2</v>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
@@ -2361,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -2403,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
@@ -2417,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -2431,7 +2431,7 @@
         <v>6</v>
       </c>
       <c r="D148">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -2445,7 +2445,7 @@
         <v>4</v>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -2459,7 +2459,7 @@
         <v>4</v>
       </c>
       <c r="D150">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -2501,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="D154">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -2529,7 +2529,7 @@
         <v>2</v>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -2599,7 +2599,7 @@
         <v>5</v>
       </c>
       <c r="D160">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -2613,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -2697,7 +2697,7 @@
         <v>2</v>
       </c>
       <c r="D167">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
@@ -2711,7 +2711,7 @@
         <v>5</v>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -2781,7 +2781,7 @@
         <v>20</v>
       </c>
       <c r="D173">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
@@ -2907,7 +2907,7 @@
         <v>1</v>
       </c>
       <c r="D182">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
@@ -2949,7 +2949,7 @@
         <v>4</v>
       </c>
       <c r="D185">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -2977,7 +2977,7 @@
         <v>3</v>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -2991,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -3005,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -3019,7 +3019,7 @@
         <v>2</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -3033,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -3061,7 +3061,7 @@
         <v>4</v>
       </c>
       <c r="D193">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
@@ -3075,7 +3075,7 @@
         <v>2</v>
       </c>
       <c r="D194">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -3103,7 +3103,7 @@
         <v>113</v>
       </c>
       <c r="D196">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -3117,7 +3117,7 @@
         <v>3</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -3187,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
@@ -3215,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="D204">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -3229,7 +3229,7 @@
         <v>22</v>
       </c>
       <c r="D205">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="D206">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
@@ -3257,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="D207">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
@@ -3285,7 +3285,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -3299,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="D210">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -3313,7 +3313,7 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -3369,7 +3369,7 @@
         <v>2</v>
       </c>
       <c r="D215">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -3383,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="D216">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -3397,7 +3397,7 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -3411,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
@@ -3453,7 +3453,7 @@
         <v>15</v>
       </c>
       <c r="D221">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -3523,7 +3523,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -3551,7 +3551,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232">
@@ -3607,7 +3607,7 @@
         <v>2</v>
       </c>
       <c r="D232">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -3621,7 +3621,7 @@
         <v>2</v>
       </c>
       <c r="D233">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234">
@@ -3635,7 +3635,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -3677,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="D237">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -3691,7 +3691,7 @@
         <v>4</v>
       </c>
       <c r="D238">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -3705,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="D239">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240">
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="241">
@@ -3747,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -3789,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -3817,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -3831,7 +3831,7 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -3845,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="D249">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -3859,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -3873,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="D251">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
@@ -3901,7 +3901,7 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -3943,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="D256">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -4041,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -4055,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="D264">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -4069,7 +4069,7 @@
         <v>4</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -4111,7 +4111,7 @@
         <v>4</v>
       </c>
       <c r="D268">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -4139,7 +4139,7 @@
         <v>2</v>
       </c>
       <c r="D270">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -4223,7 +4223,7 @@
         <v>11</v>
       </c>
       <c r="D276">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -4251,7 +4251,7 @@
         <v>1</v>
       </c>
       <c r="D278">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D280">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -4307,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -4349,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="D285">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
@@ -4377,7 +4377,7 @@
         <v>4</v>
       </c>
       <c r="D287">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -4391,7 +4391,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -4433,7 +4433,7 @@
         <v>9</v>
       </c>
       <c r="D291">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -4447,7 +4447,7 @@
         <v>41</v>
       </c>
       <c r="D292">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -4475,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -4559,7 +4559,7 @@
         <v>2</v>
       </c>
       <c r="D300">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -4587,7 +4587,7 @@
         <v>4</v>
       </c>
       <c r="D302">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -4615,7 +4615,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -4629,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="D307">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -4671,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="D308">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -4685,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="D309">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -4699,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="D310">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -4713,7 +4713,7 @@
         <v>1</v>
       </c>
       <c r="D311">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -4727,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="D312">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -4769,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -4797,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="D317">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -4811,7 +4811,7 @@
         <v>2</v>
       </c>
       <c r="D318">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="D319">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -4839,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="D320">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="D322">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -4881,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="D323">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -4895,7 +4895,7 @@
         <v>9</v>
       </c>
       <c r="D324">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -4937,7 +4937,7 @@
         <v>4</v>
       </c>
       <c r="D327">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -4965,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="D329">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330">
@@ -5049,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="D335">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -5091,7 +5091,7 @@
         <v>2</v>
       </c>
       <c r="D338">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="D339">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -5175,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -5189,7 +5189,7 @@
         <v>1</v>
       </c>
       <c r="D345">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -5203,7 +5203,7 @@
         <v>1</v>
       </c>
       <c r="D346">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -5217,7 +5217,7 @@
         <v>9</v>
       </c>
       <c r="D347">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -5315,7 +5315,7 @@
         <v>3</v>
       </c>
       <c r="D354">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="355">
@@ -5329,7 +5329,7 @@
         <v>9</v>
       </c>
       <c r="D355">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="D357">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -5385,7 +5385,7 @@
         <v>3</v>
       </c>
       <c r="D359">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="360">
@@ -5399,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="D360">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -5413,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -5427,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="D362">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="363">
@@ -5441,7 +5441,7 @@
         <v>2</v>
       </c>
       <c r="D363">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -5455,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="D364">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -5469,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="D365">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -5483,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="D366">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -5511,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="D368">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -5539,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="D370">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -5567,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="D372">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -5637,7 +5637,7 @@
         <v>11</v>
       </c>
       <c r="D377">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -5693,7 +5693,7 @@
         <v>4</v>
       </c>
       <c r="D381">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="D383">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -5735,7 +5735,7 @@
         <v>13</v>
       </c>
       <c r="D384">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -5749,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="D385">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -5777,7 +5777,7 @@
         <v>5</v>
       </c>
       <c r="D387">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
